--- a/evaluation/sheets/Step16_Cityscapes_object_metrics.xlsx
+++ b/evaluation/sheets/Step16_Cityscapes_object_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3026,6 +3026,198 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>651.68543</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.86851</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.05613</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="I41" t="n">
+        <v>42.67564</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M41" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>98.53333333333333</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.892279033916521</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R41" t="n">
+        <v>96.83333333333334</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.877198354402966</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_cfg20</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>677.2101699999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.03607</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.05665</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.05767</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.20433</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="I42" t="n">
+        <v>46.30147</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.03888</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>99.56666666666666</v>
+      </c>
+      <c r="N42" t="n">
+        <v>99.33333333333333</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9103640594918704</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R42" t="n">
+        <v>96.83333333333334</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.877198354402966</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_nocfg</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>707.90182</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.11046</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.49767</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.06433</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.24633</v>
+      </c>
+      <c r="I43" t="n">
+        <v>46.04446</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.03605</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>92.73333333333333</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.818625255336406</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R43" t="n">
+        <v>96.83333333333334</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.877198354402966</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/evaluation/sheets/Step16_Cityscapes_object_metrics.xlsx
+++ b/evaluation/sheets/Step16_Cityscapes_object_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3218,6 +3218,198 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_advbox_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>424.15187</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.72552</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.05055</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.80133</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.20933</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.77907</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.59333</v>
+      </c>
+      <c r="I44" t="n">
+        <v>22.69977</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.01155</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.0008899999999999999</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M44" t="n">
+        <v>99.46666666666667</v>
+      </c>
+      <c r="N44" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.9022106165174381</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R44" t="n">
+        <v>96.83333333333334</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.877198354402966</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_advbox_ema200000_n3000_r500_colsample_anc500_cfg20</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>401.49388</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.64435</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.05236</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.80833</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8156</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.62867</v>
+      </c>
+      <c r="I45" t="n">
+        <v>23.42256</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M45" t="n">
+        <v>99.83333333333333</v>
+      </c>
+      <c r="N45" t="n">
+        <v>99.56666666666666</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.9155158118771951</v>
+      </c>
+      <c r="P45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R45" t="n">
+        <v>96.83333333333334</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.877198354402966</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_advbox_ema200000_n3000_r500_colsample_anc500_nocfg</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>576.54538</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.44324</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.06204</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.73633</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.47233</v>
+      </c>
+      <c r="I46" t="n">
+        <v>28.9774</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M46" t="n">
+        <v>97.56666666666666</v>
+      </c>
+      <c r="N46" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.8479021287689524</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R46" t="n">
+        <v>96.83333333333334</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.877198354402966</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
